--- a/saidas/metricas_resumo/qtd/4_b_top_5/parte_3_recorte_de_marco.xlsx
+++ b/saidas/metricas_resumo/qtd/4_b_top_5/parte_3_recorte_de_marco.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>Modelo</t>
   </si>
@@ -46,46 +46,31 @@
     <t>&lt; 50%</t>
   </si>
   <si>
+    <t>SARIMA</t>
+  </si>
+  <si>
     <t>SE(LINE)+SE(SGDR)+ABR</t>
   </si>
   <si>
-    <t>SPct+ABR</t>
-  </si>
-  <si>
-    <t>SARIMA</t>
-  </si>
-  <si>
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
-    <t>SE(ABR)+MAS+OHE+ABR</t>
-  </si>
-  <si>
-    <t>SE(ETR)+MMS+BIN+SE(ELAS)+ABR</t>
-  </si>
-  <si>
     <t>11/22</t>
   </si>
   <si>
-    <t>12/22</t>
+    <t>10/22</t>
   </si>
   <si>
     <t>8/22</t>
   </si>
   <si>
-    <t>10/22</t>
+    <t>18/22</t>
   </si>
   <si>
     <t>17/22</t>
   </si>
   <si>
-    <t>18/22</t>
-  </si>
-  <si>
     <t>15/22</t>
-  </si>
-  <si>
-    <t>19/22</t>
   </si>
   <si>
     <t>22/22</t>
@@ -446,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -486,31 +471,31 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>6.61</v>
+        <v>6.46</v>
       </c>
       <c r="C2">
-        <v>8.949999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="D2">
-        <v>0.063</v>
+        <v>0.219</v>
       </c>
       <c r="E2">
-        <v>22.6</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>242.1</v>
+        <v>221</v>
       </c>
       <c r="G2">
-        <v>28.71</v>
+        <v>16.77</v>
       </c>
       <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -518,31 +503,31 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>6.1</v>
+        <v>6.54</v>
       </c>
       <c r="C3">
-        <v>8.26</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D3">
-        <v>0.178</v>
+        <v>0.108</v>
       </c>
       <c r="E3">
-        <v>14.2</v>
+        <v>18.8</v>
       </c>
       <c r="F3">
-        <v>227.2</v>
+        <v>236.3</v>
       </c>
       <c r="G3">
-        <v>22.79</v>
+        <v>27.39</v>
       </c>
       <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -550,127 +535,31 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>6.51</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="C4">
-        <v>7.82</v>
+        <v>9.68</v>
       </c>
       <c r="D4">
-        <v>0.232</v>
+        <v>-0.244</v>
       </c>
       <c r="E4">
-        <v>15.4</v>
+        <v>22.5</v>
       </c>
       <c r="F4">
-        <v>219.5</v>
+        <v>279.1</v>
       </c>
       <c r="G4">
-        <v>16.34</v>
+        <v>19.43</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="C5">
-        <v>9.68</v>
-      </c>
-      <c r="D5">
-        <v>-0.244</v>
-      </c>
-      <c r="E5">
-        <v>22.5</v>
-      </c>
-      <c r="F5">
-        <v>279.1</v>
-      </c>
-      <c r="G5">
-        <v>19.43</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>6.32</v>
-      </c>
-      <c r="C6">
-        <v>8.33</v>
-      </c>
-      <c r="D6">
-        <v>0.149</v>
-      </c>
-      <c r="E6">
-        <v>21.5</v>
-      </c>
-      <c r="F6">
-        <v>230.7</v>
-      </c>
-      <c r="G6">
-        <v>25.04</v>
-      </c>
-      <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>6.47</v>
-      </c>
-      <c r="C7">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="D7">
-        <v>0.203</v>
-      </c>
-      <c r="E7">
-        <v>-26.5</v>
-      </c>
-      <c r="F7">
-        <v>222.6</v>
-      </c>
-      <c r="G7">
-        <v>17.62</v>
-      </c>
-      <c r="H7" t="s">
         <v>19</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
